--- a/data/excel/accounts_registry.xlsx
+++ b/data/excel/accounts_registry.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$L$7</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -61,7 +62,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -424,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -505,26 +506,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5394280567</v>
+        <v>1216962667</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>spisoq</t>
+          <t>ilikebooobs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://t.me/spisoq</t>
+          <t>https://t.me/ilikebooobs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>grgrgrg</t>
+          <t>Ильяс Ильясович Ильясулы</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+77004287470</t>
+          <t>+77756277881</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -565,31 +566,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1216962667</v>
+        <v>7939104831</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ilikebooobs</t>
+          <t>kotakbaser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://t.me/ilikebooobs</t>
+          <t>https://t.me/kotakbaser</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ильяс Ильясович Ильясулы</t>
+          <t>hdhdjd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+77756277881</t>
+          <t>+77011234567</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Студент</t>
+          <t>Преподаватель</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -604,12 +605,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ВТПО 23-1</t>
+          <t>втпо 23-1</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -625,31 +626,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1216962667</v>
+        <v>5394280567</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ilikebooobs</t>
+          <t>spisoq</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://t.me/ilikebooobs</t>
+          <t>https://t.me/spisoq</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ильяс Ильясович Ильясулы</t>
+          <t>fefefefe\</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+77756277881</t>
+          <t>+77004287470</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Студент</t>
+          <t>Преподаватель</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -659,17 +660,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
+          <t>6B07155 - Электроэнергетика</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ВТПО 23-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
@@ -687,7 +688,64 @@
       <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="K6" s="2" t="n"/>
+      <c r="A6" t="n">
+        <v>5394280567</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>spisoq</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://t.me/spisoq</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fefefefe\</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+77004287470</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Преподаватель</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Инженерные технологии</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6B07155 - Электроэнергетика</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Нет ❌</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -749,71 +807,14 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7939104831</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>kotakbaser</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://t.me/kotakbaser</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>hdhdjd</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>+77011234567</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Преподаватель</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Инженерные технологии</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>втпо 23-1</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>Нет ❌</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
-  <dataValidations count="5">
-    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Выберите Да или Нет" prompt="Грантник: два клика — открыть список и выбрать" type="list">
-      <formula1>"Да,Нет"</formula1>
+  <autoFilter ref="A1:L7"/>
+  <dataValidations count="6">
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Выберите значение из списка" prompt="Грантник: Да ✅ или Нет ❌" type="list">
+      <formula1>"Да ✅,Нет ❌"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Выберите значение из списка" prompt="Грантник: Да ✅ или Нет ❌" type="list">
+      <formula1>"Да ✅,Нет ❌"</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Выберите значение из списка" prompt="Грантник: Да ✅ или Нет ❌" type="list">
       <formula1>"Да ✅,Нет ❌"</formula1>
